--- a/@serpotkine1 collection sheet.xlsx
+++ b/@serpotkine1 collection sheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="503">
   <si>
     <t>Director</t>
   </si>
@@ -827,19 +827,16 @@
     <t>All of his 31 films</t>
   </si>
   <si>
-    <t>Raoul Walsh</t>
-  </si>
-  <si>
-    <t>1915-1964</t>
-  </si>
-  <si>
-    <t>https://t.co/AA5IhlGVFo</t>
-  </si>
-  <si>
-    <t>153.08 GB</t>
-  </si>
-  <si>
-    <t>80 films</t>
+    <t>Alain Guiraudie</t>
+  </si>
+  <si>
+    <t>1990-2024</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/lCVeDxwDyDQb</t>
+  </si>
+  <si>
+    <t>16.17 GB</t>
   </si>
   <si>
     <t>Lino Brocka</t>
@@ -884,78 +881,81 @@
     <t>5 films</t>
   </si>
   <si>
-    <t>Johnnie To</t>
-  </si>
-  <si>
-    <t>1980-2020</t>
-  </si>
-  <si>
-    <t>https://transfer.it/t/XDfAWg5DxJgZ</t>
-  </si>
-  <si>
-    <t>117.67 GB</t>
+    <t>Hirokazu Kore-eda</t>
+  </si>
+  <si>
+    <t>1991-2023</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/gKN0K9oXFbbQ</t>
+  </si>
+  <si>
+    <t>51.29 GB</t>
+  </si>
+  <si>
+    <t>21 films</t>
+  </si>
+  <si>
+    <t>Tsui Hark</t>
+  </si>
+  <si>
+    <t>1979-2025</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/p2t1m54j3bzT</t>
+  </si>
+  <si>
+    <t>94.78 GB</t>
+  </si>
+  <si>
+    <t>All of his 45 films</t>
+  </si>
+  <si>
+    <t>Ringo Lam</t>
+  </si>
+  <si>
+    <t>1983-2020</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/FM2RK1hBgbyC</t>
+  </si>
+  <si>
+    <t>59.33 GB</t>
+  </si>
+  <si>
+    <t>24 films</t>
+  </si>
+  <si>
+    <t>John Woo</t>
+  </si>
+  <si>
+    <t>1969-2023</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/ZLzhjkxjyTrY</t>
+  </si>
+  <si>
+    <t>73.76 GB</t>
+  </si>
+  <si>
+    <t>36 films</t>
+  </si>
+  <si>
+    <t>George Cukor</t>
+  </si>
+  <si>
+    <t>1930-1981</t>
+  </si>
+  <si>
+    <t>transfer.it/t/ocyo6pw30TrS</t>
+  </si>
+  <si>
+    <t>92.19 GB</t>
   </si>
   <si>
     <t>56 films</t>
   </si>
   <si>
-    <t>Tsui Hark</t>
-  </si>
-  <si>
-    <t>1979-2025</t>
-  </si>
-  <si>
-    <t>https://transfer.it/t/p2t1m54j3bzT</t>
-  </si>
-  <si>
-    <t>94.78 GB</t>
-  </si>
-  <si>
-    <t>All of his 45 films</t>
-  </si>
-  <si>
-    <t>Ringo Lam</t>
-  </si>
-  <si>
-    <t>1983-2020</t>
-  </si>
-  <si>
-    <t>https://transfer.it/t/FM2RK1hBgbyC</t>
-  </si>
-  <si>
-    <t>59.33 GB</t>
-  </si>
-  <si>
-    <t>24 films</t>
-  </si>
-  <si>
-    <t>John Woo</t>
-  </si>
-  <si>
-    <t>1969-2023</t>
-  </si>
-  <si>
-    <t>https://transfer.it/t/ZLzhjkxjyTrY</t>
-  </si>
-  <si>
-    <t>73.76 GB</t>
-  </si>
-  <si>
-    <t>36 films</t>
-  </si>
-  <si>
-    <t>George Cukor</t>
-  </si>
-  <si>
-    <t>1930-1981</t>
-  </si>
-  <si>
-    <t>transfer.it/t/ocyo6pw30TrS</t>
-  </si>
-  <si>
-    <t>92.19 GB</t>
-  </si>
-  <si>
     <t>Jacques Rivette</t>
   </si>
   <si>
@@ -1295,7 +1295,20 @@
     <t>136.67 GB</t>
   </si>
   <si>
-    <t>30 films</t>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">30 films + A Tale of Filipino Violence (2022) </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <sz val="12.0"/>
+        <u/>
+      </rPr>
+      <t>transfer.it/t/FCd1SpplkBgL</t>
+    </r>
   </si>
   <si>
     <t>Zeki Demirkubuz</t>
@@ -1435,6 +1448,111 @@
   </si>
   <si>
     <t>All of his 19 films</t>
+  </si>
+  <si>
+    <t>Hong Sang-soo</t>
+  </si>
+  <si>
+    <t>1996-2026</t>
+  </si>
+  <si>
+    <t>transfer.it/t/jjVKD4h3VB4B</t>
+  </si>
+  <si>
+    <t>79.35 GB</t>
+  </si>
+  <si>
+    <t>Lucrecia Martel</t>
+  </si>
+  <si>
+    <t>1988-2025</t>
+  </si>
+  <si>
+    <t>transfer.it/t/stP3ikx3HD4C</t>
+  </si>
+  <si>
+    <t>20.18 GB</t>
+  </si>
+  <si>
+    <t>Johnnie To</t>
+  </si>
+  <si>
+    <t>1980-2020</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/XDfAWg5DxJgZ</t>
+  </si>
+  <si>
+    <t>117.67 GB</t>
+  </si>
+  <si>
+    <t>Pen-Ek Ratanaruang</t>
+  </si>
+  <si>
+    <t>1997-2017</t>
+  </si>
+  <si>
+    <t>transfer.it/t/mcG731xHwTTI</t>
+  </si>
+  <si>
+    <t>27.25 GB</t>
+  </si>
+  <si>
+    <t>Raúl Ruiz</t>
+  </si>
+  <si>
+    <t>1963-2023</t>
+  </si>
+  <si>
+    <t>https://transfer.it/t/UWW7KlpRRJob</t>
+  </si>
+  <si>
+    <t>114.01 GB</t>
+  </si>
+  <si>
+    <t>67 films</t>
+  </si>
+  <si>
+    <t>Jacques Tati</t>
+  </si>
+  <si>
+    <t>1946-1978</t>
+  </si>
+  <si>
+    <t>transfer.it/t/ebeA79pzyDhZ</t>
+  </si>
+  <si>
+    <t>21.24 GB</t>
+  </si>
+  <si>
+    <t>All of his 8 films</t>
+  </si>
+  <si>
+    <t>Alain Robbe-Grillet</t>
+  </si>
+  <si>
+    <t>1963-2006</t>
+  </si>
+  <si>
+    <t>transfer.it/t/lIgFm4x12RBD</t>
+  </si>
+  <si>
+    <t>27.96 GB</t>
+  </si>
+  <si>
+    <t>All of his 10 films</t>
+  </si>
+  <si>
+    <t>Alain Resnais</t>
+  </si>
+  <si>
+    <t>1948-2014</t>
+  </si>
+  <si>
+    <t>transfer.it/t/rRPO21pXSJaD</t>
+  </si>
+  <si>
+    <t>56.73 GB</t>
   </si>
 </sst>
 </file>
@@ -2972,7 +3090,7 @@
         <v>268</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>269</v>
@@ -2981,44 +3099,44 @@
         <v>270</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>229</v>
@@ -3026,122 +3144,122 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="F57" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="E60" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="62">
@@ -3301,7 +3419,7 @@
         <v>347</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70">
@@ -3521,7 +3639,7 @@
         <v>396</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81">
@@ -3561,7 +3679,7 @@
         <v>404</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83">
@@ -3640,7 +3758,7 @@
       <c r="E86" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F86" s="6" t="s">
         <v>423</v>
       </c>
     </row>
@@ -3681,7 +3799,7 @@
         <v>432</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="89">
@@ -3845,67 +3963,403 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="10"/>
+      <c r="A97" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="10"/>
+      <c r="A98" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="10"/>
+      <c r="A99" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="100">
-      <c r="F100" s="10"/>
+      <c r="A100" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="101">
-      <c r="F101" s="10"/>
+      <c r="A101" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="102">
-      <c r="F102" s="10"/>
+      <c r="A102" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="103">
-      <c r="F103" s="10"/>
+      <c r="A103" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="104">
-      <c r="F104" s="10"/>
+      <c r="A104" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="105">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
       <c r="F105" s="10"/>
     </row>
     <row r="106">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
       <c r="F106" s="10"/>
     </row>
     <row r="107">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
       <c r="F107" s="10"/>
     </row>
     <row r="108">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
       <c r="F108" s="10"/>
     </row>
     <row r="109">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
       <c r="F109" s="10"/>
     </row>
     <row r="110">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
       <c r="F110" s="10"/>
     </row>
     <row r="111">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
       <c r="F111" s="10"/>
     </row>
     <row r="112">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
       <c r="F112" s="10"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3995,17 +4449,26 @@
     <hyperlink r:id="rId84" ref="D84"/>
     <hyperlink r:id="rId85" ref="D85"/>
     <hyperlink r:id="rId86" ref="D86"/>
-    <hyperlink r:id="rId87" ref="D87"/>
-    <hyperlink r:id="rId88" ref="D88"/>
-    <hyperlink r:id="rId89" ref="D89"/>
-    <hyperlink r:id="rId90" ref="D90"/>
-    <hyperlink r:id="rId91" ref="D91"/>
-    <hyperlink r:id="rId92" ref="D92"/>
-    <hyperlink r:id="rId93" ref="D93"/>
-    <hyperlink r:id="rId94" ref="D94"/>
-    <hyperlink r:id="rId95" ref="D95"/>
-    <hyperlink r:id="rId96" ref="D96"/>
+    <hyperlink r:id="rId87" ref="F86"/>
+    <hyperlink r:id="rId88" ref="D87"/>
+    <hyperlink r:id="rId89" ref="D88"/>
+    <hyperlink r:id="rId90" ref="D89"/>
+    <hyperlink r:id="rId91" ref="D90"/>
+    <hyperlink r:id="rId92" ref="D91"/>
+    <hyperlink r:id="rId93" ref="D92"/>
+    <hyperlink r:id="rId94" ref="D93"/>
+    <hyperlink r:id="rId95" ref="D94"/>
+    <hyperlink r:id="rId96" ref="D95"/>
+    <hyperlink r:id="rId97" ref="D96"/>
+    <hyperlink r:id="rId98" ref="D97"/>
+    <hyperlink r:id="rId99" ref="D98"/>
+    <hyperlink r:id="rId100" ref="D99"/>
+    <hyperlink r:id="rId101" ref="D100"/>
+    <hyperlink r:id="rId102" ref="D101"/>
+    <hyperlink r:id="rId103" ref="D102"/>
+    <hyperlink r:id="rId104" ref="D103"/>
+    <hyperlink r:id="rId105" ref="D104"/>
   </hyperlinks>
-  <drawing r:id="rId97"/>
+  <drawing r:id="rId106"/>
 </worksheet>
 </file>